--- a/artfynd/A 1917-2023 artfynd.xlsx
+++ b/artfynd/A 1917-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 1917-2023 artfynd.xlsx
+++ b/artfynd/A 1917-2023 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>93574777</v>
+        <v>93574776</v>
       </c>
       <c r="B2" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56884</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>208255</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Zootoca vivipara</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Jacquin, 1787)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>ca 1km NNV Blomhult, Sm</t>
+          <t>ca 900m NNV Blomhult, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>536311.7164625528</v>
+        <v>536283</v>
       </c>
       <c r="R2" t="n">
-        <v>6321190.874822649</v>
+        <v>6320991</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,19 +743,9 @@
           <t>2021-05-12</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-05-12</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,7 +759,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -785,22 +770,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ola Hammarström, Ola Bengtsson</t>
+          <t>Ola Bengtsson, Ola Hammarström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>93574776</v>
+        <v>93574777</v>
       </c>
       <c r="B3" t="n">
-        <v>55649</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,37 +788,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208255</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Zootoca vivipara</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Jacquin, 1787)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>ca 900m NNV Blomhult, Sm</t>
+          <t>ca 1km NNV Blomhult, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>536282.9276682498</v>
+        <v>536311</v>
       </c>
       <c r="R3" t="n">
-        <v>6320991.45110261</v>
+        <v>6321191</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -865,19 +845,9 @@
           <t>2021-05-12</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-05-12</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -891,7 +861,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -902,7 +872,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ola Hammarström, Ola Bengtsson</t>
+          <t>Ola Bengtsson, Ola Hammarström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
